--- a/datos_de_prueba/Ejemplo de carga masiva.xlsx
+++ b/datos_de_prueba/Ejemplo de carga masiva.xlsx
@@ -595,7 +595,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1257,7 +1257,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">

--- a/datos_de_prueba/Ejemplo de carga masiva.xlsx
+++ b/datos_de_prueba/Ejemplo de carga masiva.xlsx
@@ -7,18 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Matriz-Req-Inf" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Oficios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oficios'!$A$1:$AA$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -30,7 +30,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,12 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,940 +427,1030 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="33" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Referencia UDC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Institución del Estado</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Fecha Asignación</t>
+          <t>Referencia oficio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Usuario</t>
+          <t>Tipo de acción</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Causal oficio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de oficio</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de recepción</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de asignación</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha de respuesta</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cantidad de investigados</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha Emisión</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Referencia</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Medio Repuesta</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha Envío</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Usuario responsable</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Días</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Canal Recepc</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha Circular</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Apellidos, Nombres - Razón Social</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>TiPASo Id CED; PAS; RUCUC</t>
+          <t>Documento del oficio</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Identificación Ced; Pas; RUC</t>
+          <t>Respuesta en PDF</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Referencia - Oficio FGE; Juzgado</t>
+          <t>Observación</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Número Expediente Fiscal</t>
+          <t>Registrado por</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Referencia - Circular Superintendencia Bancos</t>
+          <t>Fecha de registro</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Delito</t>
+          <t>Origen</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Accion</t>
+          <t>Anulado</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Observación</t>
+          <t>Motivo de anulación</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de Implicado</t>
+          <t>Implicado</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>LCI - SI o NO</t>
+          <t>Tipo de identificación</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Fecha - Solicitud</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Ref Solic- No. LCI-202X-000</t>
+          <t>Tipo de implicado</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>LCI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JUL</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>46226</v>
+          <t>Superintendencia de Bancos</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SB-2026-0101-OF</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C. Roman</t>
+          <t>Certificación</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>LAVADO DE ACTIVOS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>46225</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Electrónico</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>cmroman</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Camila Maria Roman Townsed</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>46221</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Atendido dentro del plazo</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
         <is>
           <t>ORDOÑEZ VILLAGOMEZ DAVID MIGUEL</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>CED</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Cédula</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>1400349096</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>SB-2026-0101-OF</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>LAVADO DE ACTIVOS</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>CERTIFICACIÓN</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Atendido dentro del plazo</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>CLIENTE</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="n">
-        <v>46226</v>
-      </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>LCI-2026-001</t>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FGE</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>46246</v>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FPP-FED4-2026-000123-O</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>J. Portero</t>
+          <t>Retención</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>COHECHO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Electrónico</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>jportero</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Joel Tyrone Portero Cervantes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>En proceso</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ACOSTA JEREZ DIANA CAROLINA</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>CED</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0923847561</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>FPP-FED4-2026-000123-O</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>COHECHO</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>RETENCIÓN</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>CLIENTE</t>
+          <t>ACOSTA JEREZ DIANA CAROLINA</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>46246</v>
+          <t>Cédula</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0923847561</t>
+        </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>LCI-2026-001</t>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FGE</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>46246</v>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FPP-FED4-2026-000123-O</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>J. Portero</t>
+          <t>Retención</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>COHECHO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Electrónico</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>jportero</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Joel Tyrone Portero Cervantes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>En proceso</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>MENDOZA SALAS LUIS ALBERTO</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>CED</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1712345678</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>FPP-FED4-2026-000123-O</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>COHECHO</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>RETENCIÓN</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>EX CLIENTE</t>
+          <t>MENDOZA SALAS LUIS ALBERTO</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>46246</v>
+          <t>Cédula</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1712345678</t>
+        </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>LCI-2026-001</t>
+          <t>Ex cliente</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>FGE</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>46246</v>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FPP-FED4-2026-000123-O</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>J. Portero</t>
+          <t>Retención</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>46245</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>COHECHO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Electrónico</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>jportero</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Joel Tyrone Portero Cervantes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>En proceso</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>PARRA NUÑEZ SOFIA ELENA</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>CED</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0102938475</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>FPP-FED4-2026-000123-O</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>COHECHO</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>RETENCIÓN</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>NO CLIENTE</t>
+          <t>QUISPE ANDRADE PEDRO JOSÉ</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="n">
-        <v>46246</v>
+          <t>Pasaporte</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>AB123456</t>
+        </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>LCI-2026-001</t>
+          <t>No cliente</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>Superintendencia de Bancos</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SB-2026-0118-OF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Información</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>46261</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Electrónico</t>
-        </is>
-      </c>
+          <t>DEFRAUDACIÓN TRIBUTARIA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>Por asignar</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>46258</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Pendiente de asignar</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
         <is>
           <t>CEVALLOS MORA JORGE ANDRÉS</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>CED</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Cédula</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>1309876543</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>SB-2026-0118-OF</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>DEFRAUDACIÓN TRIBUTARIA</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>INFORMACIÓN</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Pendiente de asignar</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SIN IDENTIFICACION</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="n">
-        <v>46262</v>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>LCI-2026-001</t>
+          <t>Sin identificación</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SB</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>46254</v>
+          <t>Superintendencia de Bancos</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SB-2026-0125-OF</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>L. Jarrin</t>
+          <t>Bloqueo y retención</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>ENRIQUECIMIENTO ILÍCITO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>46254</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Electrónico</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>46263</v>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>lgjarrin</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Lizzi Gabriela Jarrin Aguilar</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Finalizado</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>46251</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Se remitió por correo</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
         <is>
           <t>COMERCIAL LOS ANDES S.A.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>RUC</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>1791234567001</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>SB-2026-0125-OF</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>ENRIQUECIMIENTO ILÍCITO</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>BLOQUEO Y RETENCIÓN</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Se remitió por correo</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>CLIENTE</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="n">
-        <v>46255</v>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>LCI-2026-001</t>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FGE</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>46257</v>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FPP-FED4-2026-000188-O</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>D. Franco</t>
+          <t>Levantamiento</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>46256</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>TRAFICO ILÍCITO DE SUSTANCIAS CATALOGADAS SUJETAS A FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Electrónico</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>dtfranco</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Damara Tais Franco Pacheco</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>En proceso</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>QUISPE ANDRADE PEDRO JOSÉ</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>PAS</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>AB123456</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>FPP-FED4-2026-000188-O</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>TRAFICO ILÍCITO DE SUSTANCIAS CATALOGADAS SUJETAS A FISCALIZACIÓN</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>LEVANTAMIENTO DE MEDIDAS</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>NO CLIENTE</t>
+          <t>VILLACÍS ROJAS ANDREA PAOLA</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="n">
-        <v>46257</v>
+          <t>Cédula</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0102938475</t>
+        </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>LCI-2026-001</t>
-        </is>
-      </c>
+          <t>No cliente</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FPP-FED4-2026-000188-O</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Levantamiento</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TRAFICO ILÍCITO DE SUSTANCIAS CATALOGADAS SUJETAS A FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>dtfranco</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Damara Tais Franco Pacheco</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>En proceso</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ZAMBRANO LOOR KEVIN DANIEL</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Cédula</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1301122334</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FPP-FED2-2026-000204-O</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Inmovilización</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PECULADO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Por asignar</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Llegó sin el detalle de las personas</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AA10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/datos_de_prueba/Ejemplo de carga masiva.xlsx
+++ b/datos_de_prueba/Ejemplo de carga masiva.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Oficios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oficios'!$A$1:$AA$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Oficios'!$A$1:$Z$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,343 +427,336 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="38" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="33" customWidth="1" min="23" max="23"/>
-    <col width="24" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="5" customWidth="1" min="27" max="27"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="38" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="33" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Referencia UDC</t>
+          <t>Institución del Estado</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Institución del Estado</t>
+          <t>Referencia oficio</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Referencia oficio</t>
+          <t>Tipo de acción</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de acción</t>
+          <t>Causal oficio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Causal oficio</t>
+          <t>Fecha de oficio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Fecha de oficio</t>
+          <t>Fecha de recepción</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Fecha de recepción</t>
+          <t>Fecha de asignación</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Fecha de asignación</t>
+          <t>Fecha de respuesta</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Fecha de respuesta</t>
+          <t>Cantidad de investigados</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Cantidad de investigados</t>
+          <t>Prioridad</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Prioridad</t>
+          <t>Usuario responsable</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Usuario responsable</t>
+          <t>Responsable</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Responsable</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Documento del oficio</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Documento del oficio</t>
+          <t>Respuesta en PDF</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Respuesta en PDF</t>
+          <t>Observación</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Observación</t>
+          <t>Registrado por</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Registrado por</t>
+          <t>Fecha de registro</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Fecha de registro</t>
+          <t>Origen</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Origen</t>
+          <t>Anulado</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Anulado</t>
+          <t>Motivo de anulación</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Motivo de anulación</t>
+          <t>Implicado</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Implicado</t>
+          <t>Tipo de identificación</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Tipo de identificación</t>
+          <t>Identificación</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Identificación</t>
+          <t>Tipo de implicado</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de implicado</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>LCI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Superintendencia de Bancos</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB-2026-0101-OF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SB-2026-0101-OF</t>
+          <t>Certificación</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Certificación</t>
+          <t>LAVADO DE ACTIVOS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LAVADO DE ACTIVOS</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>cmroman</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>cmroman</t>
+          <t>Camila Maria Roman Townsed</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Camila Maria Roman Townsed</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
           <t>Finalizado</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Atendido dentro del plazo</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>ORDOÑEZ VILLAGOMEZ DAVID MIGUEL</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>ORDOÑEZ VILLAGOMEZ DAVID MIGUEL</t>
+          <t>Cédula</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Cédula</t>
+          <t>1400349096</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1400349096</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FPP-FED4-2026-000123-O</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FPP-FED4-2026-000123-O</t>
+          <t>Retención</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Retención</t>
+          <t>COHECHO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>COHECHO</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>jportero</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>jportero</t>
+          <t>Joel Tyrone Portero Cervantes</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Joel Tyrone Portero Cervantes</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
           <t>En proceso</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -771,96 +764,95 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>ACOSTA JEREZ DIANA CAROLINA</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>ACOSTA JEREZ DIANA CAROLINA</t>
+          <t>Cédula</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Cédula</t>
+          <t>0923847561</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0923847561</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FPP-FED4-2026-000123-O</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FPP-FED4-2026-000123-O</t>
+          <t>Retención</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Retención</t>
+          <t>COHECHO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COHECHO</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>jportero</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>jportero</t>
+          <t>Joel Tyrone Portero Cervantes</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Joel Tyrone Portero Cervantes</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
           <t>En proceso</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -868,96 +860,95 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>MENDOZA SALAS LUIS ALBERTO</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>MENDOZA SALAS LUIS ALBERTO</t>
+          <t>Cédula</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Cédula</t>
+          <t>1712345678</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1712345678</t>
+          <t>Ex cliente</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
-        <is>
-          <t>Ex cliente</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FPP-FED4-2026-000123-O</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FPP-FED4-2026-000123-O</t>
+          <t>Retención</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Retención</t>
+          <t>COHECHO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COHECHO</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>jportero</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>jportero</t>
+          <t>Joel Tyrone Portero Cervantes</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Joel Tyrone Portero Cervantes</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
           <t>En proceso</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -965,290 +956,287 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>QUISPE ANDRADE PEDRO JOSÉ</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>QUISPE ANDRADE PEDRO JOSÉ</t>
+          <t>Pasaporte</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Pasaporte</t>
+          <t>AB123456</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>AB123456</t>
+          <t>No cliente</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
-        <is>
-          <t>No cliente</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Superintendencia de Bancos</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB-2026-0118-OF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SB-2026-0118-OF</t>
+          <t>Información</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Información</t>
+          <t>DEFRAUDACIÓN TRIBUTARIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEFRAUDACIÓN TRIBUTARIA</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
           <t>Baja</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Por asignar</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Pendiente de asignar</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>CEVALLOS MORA JORGE ANDRÉS</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>CEVALLOS MORA JORGE ANDRÉS</t>
+          <t>Cédula</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Cédula</t>
+          <t>1309876543</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1309876543</t>
+          <t>Sin identificación</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
-        <is>
-          <t>Sin identificación</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Superintendencia de Bancos</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Superintendencia de Bancos</t>
+          <t>SB-2026-0125-OF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SB-2026-0125-OF</t>
+          <t>Bloqueo y retención</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bloqueo y retención</t>
+          <t>ENRIQUECIMIENTO ILÍCITO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ENRIQUECIMIENTO ILÍCITO</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>lgjarrin</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>lgjarrin</t>
+          <t>Lizzi Gabriela Jarrin Aguilar</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Lizzi Gabriela Jarrin Aguilar</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
           <t>Finalizado</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Se remitió por correo</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>COMERCIAL LOS ANDES S.A.</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>COMERCIAL LOS ANDES S.A.</t>
+          <t>RUC</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>RUC</t>
+          <t>1791234567001</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1791234567001</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FPP-FED4-2026-000188-O</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FPP-FED4-2026-000188-O</t>
+          <t>Levantamiento</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Levantamiento</t>
+          <t>TRAFICO ILÍCITO DE SUSTANCIAS CATALOGADAS SUJETAS A FISCALIZACIÓN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TRAFICO ILÍCITO DE SUSTANCIAS CATALOGADAS SUJETAS A FISCALIZACIÓN</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>dtfranco</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>dtfranco</t>
+          <t>Damara Tais Franco Pacheco</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Damara Tais Franco Pacheco</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
           <t>En proceso</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1256,96 +1244,95 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>VILLACÍS ROJAS ANDREA PAOLA</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>VILLACÍS ROJAS ANDREA PAOLA</t>
+          <t>Cédula</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Cédula</t>
+          <t>0102938475</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0102938475</t>
+          <t>No cliente</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
-        <is>
-          <t>No cliente</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FPP-FED4-2026-000188-O</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FPP-FED4-2026-000188-O</t>
+          <t>Levantamiento</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Levantamiento</t>
+          <t>TRAFICO ILÍCITO DE SUSTANCIAS CATALOGADAS SUJETAS A FISCALIZACIÓN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TRAFICO ILÍCITO DE SUSTANCIAS CATALOGADAS SUJETAS A FISCALIZACIÓN</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>dtfranco</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>dtfranco</t>
+          <t>Damara Tais Franco Pacheco</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Damara Tais Franco Pacheco</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
           <t>En proceso</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1353,91 +1340,90 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ZAMBRANO LOOR KEVIN DANIEL</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>ZAMBRANO LOOR KEVIN DANIEL</t>
+          <t>Cédula</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Cédula</t>
+          <t>1301122334</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1301122334</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fiscalía General del Estado</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiscalía General del Estado</t>
+          <t>FPP-FED2-2026-000204-O</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FPP-FED2-2026-000204-O</t>
+          <t>Inmovilización</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Inmovilización</t>
+          <t>PECULADO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PECULADO</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
           <t>Media</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Por asignar</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Llegó sin el detalle de las personas</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -1447,10 +1433,9 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA10"/>
+  <autoFilter ref="A1:Z10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>